--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,12 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>97308</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>99592</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R2" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S2" t="n">
         <v>100</v>
@@ -753,19 +748,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -804,12 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>96254</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98499</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -837,10 +817,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R3" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S3" t="n">
         <v>100</v>
@@ -875,19 +855,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,12 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>96356</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98602</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -963,10 +928,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R4" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S4" t="n">
         <v>100</v>
@@ -1001,19 +966,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1052,12 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>96237</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98483</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1089,10 +1039,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R5" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1127,19 +1077,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1178,12 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>96354</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>98600</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1215,10 +1150,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R6" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S6" t="n">
         <v>100</v>
@@ -1253,19 +1188,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1304,12 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>95519</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97454</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1341,10 +1261,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>532068.5715857567</v>
+        <v>532069</v>
       </c>
       <c r="R7" t="n">
-        <v>6822081.209926664</v>
+        <v>6822081</v>
       </c>
       <c r="S7" t="n">
         <v>100</v>
@@ -1379,19 +1299,9 @@
           <t>1987-08-29</t>
         </is>
       </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA7" t="inlineStr">
         <is>
           <t>1987-08-29</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99592</v>
+        <v>99598</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98499</v>
+        <v>98505</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98602</v>
+        <v>98608</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98483</v>
+        <v>98489</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98600</v>
+        <v>98606</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97454</v>
+        <v>97460</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99598</v>
+        <v>99601</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98505</v>
+        <v>98508</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98608</v>
+        <v>98611</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98489</v>
+        <v>98492</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98606</v>
+        <v>98609</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97460</v>
+        <v>97462</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99601</v>
+        <v>99606</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98508</v>
+        <v>98511</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98611</v>
+        <v>98614</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98492</v>
+        <v>98495</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98609</v>
+        <v>98612</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99606</v>
+        <v>99607</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98511</v>
+        <v>98512</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98614</v>
+        <v>98615</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98495</v>
+        <v>98496</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98612</v>
+        <v>98613</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97462</v>
+        <v>97463</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99607</v>
+        <v>99634</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98512</v>
+        <v>98539</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98615</v>
+        <v>98642</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98496</v>
+        <v>98523</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98613</v>
+        <v>98640</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97463</v>
+        <v>97490</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99634</v>
+        <v>99640</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98539</v>
+        <v>98545</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98642</v>
+        <v>98648</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98523</v>
+        <v>98529</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98640</v>
+        <v>98646</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97490</v>
+        <v>97496</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99640</v>
+        <v>99647</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98545</v>
+        <v>98552</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98648</v>
+        <v>98655</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98529</v>
+        <v>98536</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98646</v>
+        <v>98653</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97496</v>
+        <v>97503</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99647</v>
+        <v>99651</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98552</v>
+        <v>98556</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98655</v>
+        <v>98659</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98536</v>
+        <v>98540</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98653</v>
+        <v>98657</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97503</v>
+        <v>97507</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99651</v>
+        <v>99658</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98556</v>
+        <v>98563</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98659</v>
+        <v>98666</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98540</v>
+        <v>98547</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98657</v>
+        <v>98664</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97507</v>
+        <v>97514</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99661</v>
+        <v>99666</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98566</v>
+        <v>98571</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98669</v>
+        <v>98674</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98550</v>
+        <v>98555</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98667</v>
+        <v>98672</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97517</v>
+        <v>97522</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>84121741</v>
       </c>
       <c r="B2" t="n">
-        <v>99666</v>
+        <v>99674</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -789,7 +789,7 @@
         <v>84121764</v>
       </c>
       <c r="B3" t="n">
-        <v>98571</v>
+        <v>98579</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -896,7 +896,7 @@
         <v>84121762</v>
       </c>
       <c r="B4" t="n">
-        <v>98674</v>
+        <v>98682</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1007,7 +1007,7 @@
         <v>84121765</v>
       </c>
       <c r="B5" t="n">
-        <v>98555</v>
+        <v>98563</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1118,7 +1118,7 @@
         <v>84121763</v>
       </c>
       <c r="B6" t="n">
-        <v>98672</v>
+        <v>98680</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1229,7 +1229,7 @@
         <v>84121778</v>
       </c>
       <c r="B7" t="n">
-        <v>97522</v>
+        <v>97530</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>

--- a/artfynd/A 24085-2024 artfynd.xlsx
+++ b/artfynd/A 24085-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY7"/>
+  <dimension ref="A1:AY8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1330,6 +1330,113 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr">
+        <is>
+          <t>Hälsinglands flora (2019)</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>84121780</v>
+      </c>
+      <c r="B8" t="n">
+        <v>97524</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>221944</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Lopplummer (aggregat)</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Huperzia selago agg.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr"/>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Långasen,  200 m SO om, Hls</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>532069</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6822081</v>
+      </c>
+      <c r="S8" t="n">
+        <v>100</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Gävleborg</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Hälsingland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ovanåker</t>
+        </is>
+      </c>
+      <c r="X8" t="inlineStr">
+        <is>
+          <t>SOL198708291120</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>1987-08-29</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>1987-08-29</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>Skogskärr med bäck</t>
+        </is>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Björn Wannberg</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Stefan Olander</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
         <is>
           <t>Hälsinglands flora (2019)</t>
         </is>
